--- a/高经济价值第六期_加盟商准入续约/加盟商准入续约_v1_题目.xlsx
+++ b/高经济价值第六期_加盟商准入续约/加盟商准入续约_v1_题目.xlsx
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>准入只看资金实力，忽略选址和合规</t>
+          <t>这个加盟商资金实力很强，选址和合规差点也没关系，先放进来</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>四维度加权评分缺一不可</t>
+          <t>准入须四维度加权评分，缺一不可</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>有违规记录的加盟商直接拒绝，不考虑整改</t>
+          <t>只要有违规记录就直接拒，不用给整改机会</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>续约评级只看营收达成，忽略食安和客诉</t>
+          <t>续约就看营收达没达标，食安客诉不用看</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>须四项标准同时满足</t>
+          <t>续约评级须四项标准同时满足，就低判定</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>授权费按固定价收取，不看城市和商圈</t>
+          <t>授权费统一按500元/㎡收，别搞什么城市商圈系数</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>须按城市系数和商圈系数调整</t>
+          <t>授权费须按城市系数和商圈系数调整</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>保证金可以充抵货款</t>
+          <t>保证金先用来抵货款，后面再补</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D级门店直接收回，不给整改期</t>
+          <t>D级门店马上收回，别给整改期</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>D级是合同到期后不续约，收回需按合同执行</t>
+          <t>D级是合同到期后不续约，收回须按合同执行</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>供应链毛利按门店营业额计提</t>
+          <t>公司从加盟店赚的钱按营业额提成就行</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>应按门店食材采购额计算</t>
+          <t>供应链毛利应按门店食材采购额计算</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>客诉率按投诉次数直接算，不按订单数</t>
+          <t>客诉率直接数投诉次数，不用除以订单量</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>须除以年度订单数</t>
+          <t>客诉率须采用订单数口径</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>巡店评分可由加盟商自评</t>
+          <t>巡店评分让加盟商自己填一下</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>须由公司巡店人员评定</t>
+          <t>巡店评分须由公司巡店人员评定</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>合同到期前无需提前通知续约</t>
+          <t>合同到期再说续约的事，不用提前通知</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>新加盟商可以免保证金</t>
+          <t>新加盟商是自己人，保证金免了</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>保证金为强制条款</t>
+          <t>保证金为强制条款，不得免除</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>加盟门店亏损由公司补贴</t>
+          <t>加盟店亏损公司补一下，别让加盟商跑了</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
